--- a/data/I GST.xlsx
+++ b/data/I GST.xlsx
@@ -25,88 +25,16 @@
     <t xml:space="preserve">TAX INVOICE</t>
   </si>
   <si>
-    <t xml:space="preserve"> ADOODS GARMENTS </t>
+    <t xml:space="preserve"> Max GARMENTS </t>
   </si>
   <si>
     <t xml:space="preserve">ALL KINDS OF T-SHIRT MANUFACTURE</t>
   </si>
   <si>
-    <t xml:space="preserve">88-1/50M, 1st FLOOR NEAR SRINIVASA THEATRE, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULAVARSANDHAI ROAD, HOSUR - 635 109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTIN :33DJRPP6135G1ZW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATE: TAMIL NADU   CODE: 33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                           Website : adoodshosur@gmail.com                   PHONE:-   9514109080 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                                     Email : sales@adoods.com                                     6382208004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUYER DETAILS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVOICE DETAILS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Sairam college of Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVOICE NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 11 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.O NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gst no: 
-E. &amp; O.E
-ADVANSH 
-D
-E. &amp; O.E
-ADVANSH 
-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL.NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description of Goods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSN/SAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T SHIRT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOS</t>
+    <t xml:space="preserve">882/50M, 1st FLOOR NEAR Vijay THEATRE, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULAVARSANDHAI ROAD, chennai – 600 000</t>
   </si>
   <si>
     <r>
@@ -117,7 +45,108 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">ADVANSH</t>
+      <t xml:space="preserve">GSTIN :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P6135G1ZW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">33DJRP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STATE: TAMIL NADU   CODE: 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                           Website : Example.com                   PHONE:-   900000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                     Email : sales@example.com                                     6000000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUYER DETAILS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVOICE DETAILS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri stalin college of Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVOICE NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 11 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.O NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gst no: 
+E. &amp; O.E
+ADVANSH 
+D
+E. &amp; O.E
+ADVANSH 
+D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL.NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of Goods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSN/SAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T SHIRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Black"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">STALIN</t>
     </r>
     <r>
       <rPr>
@@ -163,7 +192,7 @@
     <t xml:space="preserve">Tax Amount (in words) :</t>
   </si>
   <si>
-    <t xml:space="preserve">GP  :-9514109080 _6382208004</t>
+    <t xml:space="preserve">GP  :-9000000000 _6000000004</t>
   </si>
   <si>
     <t xml:space="preserve">BANK DETAILS:                </t>
@@ -196,7 +225,7 @@
     <t xml:space="preserve">Declaration</t>
   </si>
   <si>
-    <t xml:space="preserve">for ADOODS GARMENTS</t>
+    <t xml:space="preserve">for Example GARMENTS</t>
   </si>
   <si>
     <t xml:space="preserve">We declare that the Invoice shows the actual price of the goods</t>
@@ -218,7 +247,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -262,6 +291,13 @@
       <name val="Arial Black"/>
       <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Black"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -518,7 +554,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -571,7 +607,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -603,7 +639,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -631,7 +667,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -667,7 +703,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -735,7 +771,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -751,19 +787,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -786,13 +814,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>257040</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>266400</xdr:colOff>
+      <xdr:colOff>265680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>174960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -806,7 +834,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10837440" y="12677760"/>
-          <a:ext cx="9360" cy="9360"/>
+          <a:ext cx="8640" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1173,7 +1201,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="19"/>
     </row>
-    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="n">
         <v>9</v>
       </c>
@@ -1483,11 +1511,11 @@
       <c r="H47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="59" t="s">
+      <c r="A48" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="60"/>
-      <c r="C48" s="60"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
@@ -1514,11 +1542,11 @@
       <c r="C50" s="48"/>
       <c r="D50" s="48"/>
       <c r="E50" s="48"/>
-      <c r="F50" s="61" t="s">
+      <c r="F50" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -1568,6 +1596,9 @@
     <mergeCell ref="F48:H49"/>
     <mergeCell ref="F50:H50"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A9" r:id="rId1" display="                                                                     Email : sales@example.com                                     6000000000"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="50" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1575,6 +1606,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>